--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Domain_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Domain_by_Sample_Layer.xlsx
@@ -470,7 +470,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.959136224599615</v>
+        <v>0.959269235930841</v>
       </c>
     </row>
   </sheetData>
@@ -506,10 +506,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999994</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.88617442332007</v>
+        <v>99.9999999999996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.886146477372317</v>
       </c>
     </row>
   </sheetData>
@@ -584,10 +584,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>100.000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.16189943992349</v>
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.16188127510509</v>
       </c>
     </row>
   </sheetData>
@@ -623,40 +623,79 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.93884203323208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
         <v>99.9999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9388349696643</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>7</v>
+        <v>3.84734909467346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -665,37 +704,154 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>3.84607666831699</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>8</v>
+        <v>2.29080564115035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.45593627066706</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>99.9999999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.724399176143394</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.0251995654712</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -704,37 +860,37 @@
         <v>99.9999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.29091121830424</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>9</v>
+        <v>7.09131735935768</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -743,163 +899,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1.45593627066706</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.724248613832731</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23.0252001632202</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7.08998682749416</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>99.9999999999997</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.897185476971897</v>
+        <v>0.897231285234919</v>
       </c>
     </row>
   </sheetData>
